--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T07:37:23+00:00</t>
+    <t>2024-10-25T08:22:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T08:22:33+00:00</t>
+    <t>2024-10-28T11:11:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T11:11:19+00:00</t>
+    <t>2024-10-28T11:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T11:26:59+00:00</t>
+    <t>2024-10-29T09:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T09:20:35+00:00</t>
+    <t>2024-10-31T11:17:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T11:17:53+00:00</t>
+    <t>2024-10-31T15:29:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T15:29:56+00:00</t>
+    <t>2024-11-05T14:48:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T14:48:02+00:00</t>
+    <t>2024-11-07T21:06:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T21:06:19+00:00</t>
+    <t>2024-11-07T21:57:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T21:57:27+00:00</t>
+    <t>2024-11-07T22:09:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-09T09:07:40+00:00</t>
+    <t>2024-11-11T13:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:26:20+00:00</t>
+    <t>2024-11-12T06:42:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:42:28+00:00</t>
+    <t>2024-11-12T07:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:20:07+00:00</t>
+    <t>2024-11-12T07:35:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:35:41+00:00</t>
+    <t>2024-11-12T07:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:42:03+00:00</t>
+    <t>2024-11-12T08:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:38:00+00:00</t>
+    <t>2024-11-12T08:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:47:06+00:00</t>
+    <t>2024-11-12T20:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T20:06:39+00:00</t>
+    <t>2024-11-14T06:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T06:51:52+00:00</t>
+    <t>2024-11-14T14:31:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:31:22+00:00</t>
+    <t>2024-11-14T14:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:34:15+00:00</t>
+    <t>2024-11-14T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:43:46+00:00</t>
+    <t>2024-11-15T18:55:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T18:55:56+00:00</t>
+    <t>2024-11-15T19:04:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:04:50+00:00</t>
+    <t>2024-11-15T19:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:21:45+00:00</t>
+    <t>2024-11-15T20:14:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T20:14:47+00:00</t>
+    <t>2024-11-17T19:44:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:44:33+00:00</t>
+    <t>2024-11-19T10:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-moped-ext-VerdachtFremdverschulden.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-19T10:30:26+00:00</t>
+    <t>2025-02-10T09:28:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
